--- a/query3_results.xlsx
+++ b/query3_results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5285cb0be836e74d/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5285cb0be836e74d/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{59ED60B4-7889-4CCA-832B-EB926E9DF417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9AC1A53-CB71-4C45-B056-05A1A663EC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="2280" windowWidth="21600" windowHeight="11295" xr2:uid="{1B85ADEC-AB39-460E-90A9-1EE8DF40A2A4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2D8F7FF3-3BD9-429C-8996-96DBC34F5592}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>stake_level</t>
   </si>
@@ -44,16 +47,25 @@
     <t>contests</t>
   </si>
   <si>
+    <t>total_invested</t>
+  </si>
+  <si>
+    <t>total_winnings</t>
+  </si>
+  <si>
     <t>total_profit</t>
   </si>
   <si>
-    <t>avg_roi_pct</t>
-  </si>
-  <si>
-    <t>worst_roi</t>
-  </si>
-  <si>
-    <t>best_roi</t>
+    <t>portfolio_roi_pct</t>
+  </si>
+  <si>
+    <t>avg_entry_roi_pct</t>
+  </si>
+  <si>
+    <t>worst_entry_roi</t>
+  </si>
+  <si>
+    <t>best_entry_roi</t>
   </si>
   <si>
     <t>Premium ($100+)</t>
@@ -440,17 +452,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC5B7702-2975-46CA-B3D2-87EB6D3FA603}">
-  <dimension ref="A1:F5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C86F568B-07C7-4A64-A1EE-DBC1E06FCB17}">
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -469,84 +486,129 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B2">
         <v>293</v>
       </c>
       <c r="C2" s="1">
+        <v>52749</v>
+      </c>
+      <c r="D2" s="1">
+        <v>113019.22</v>
+      </c>
+      <c r="E2" s="1">
         <v>60270.22</v>
       </c>
-      <c r="D2">
+      <c r="F2">
+        <v>114.26</v>
+      </c>
+      <c r="G2">
         <v>78.48</v>
       </c>
-      <c r="E2">
+      <c r="H2">
         <v>-100</v>
       </c>
-      <c r="F2">
+      <c r="I2">
         <v>14915.02</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3">
         <v>9188</v>
       </c>
       <c r="C3" s="1">
+        <v>77703.990000000005</v>
+      </c>
+      <c r="D3" s="1">
+        <v>126745.92</v>
+      </c>
+      <c r="E3" s="1">
         <v>49041.93</v>
       </c>
-      <c r="D3">
+      <c r="F3">
+        <v>63.11</v>
+      </c>
+      <c r="G3">
         <v>63.49</v>
       </c>
-      <c r="E3">
+      <c r="H3">
         <v>-100</v>
       </c>
-      <c r="F3">
+      <c r="I3">
         <v>312400</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>18060</v>
       </c>
       <c r="C4" s="1">
+        <v>28106.1</v>
+      </c>
+      <c r="D4" s="1">
+        <v>32569.61</v>
+      </c>
+      <c r="E4" s="1">
         <v>4463.51</v>
       </c>
-      <c r="D4">
+      <c r="F4">
+        <v>15.88</v>
+      </c>
+      <c r="G4">
         <v>33.54</v>
       </c>
-      <c r="E4">
+      <c r="H4">
         <v>-100</v>
       </c>
-      <c r="F4">
+      <c r="I4">
         <v>499900</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B5">
         <v>825</v>
       </c>
       <c r="C5" s="1">
+        <v>22833.8</v>
+      </c>
+      <c r="D5" s="1">
+        <v>22729.64</v>
+      </c>
+      <c r="E5" s="1">
         <v>-104.16</v>
       </c>
-      <c r="D5">
+      <c r="F5">
+        <v>-0.46</v>
+      </c>
+      <c r="G5">
         <v>5.17</v>
       </c>
-      <c r="E5">
+      <c r="H5">
         <v>-100</v>
       </c>
-      <c r="F5">
+      <c r="I5">
         <v>1775</v>
       </c>
     </row>
